--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLarge.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLarge.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>财务期间</t>
   </si>
@@ -104,6 +104,9 @@
     <t>运费币种</t>
   </si>
   <si>
+    <t>账单总金额</t>
+  </si>
+  <si>
     <t>头程预估运费（含税）</t>
   </si>
   <si>
@@ -152,6 +155,9 @@
     <t>目的港杂费付款时间</t>
   </si>
   <si>
+    <t>关税计算系数</t>
+  </si>
+  <si>
     <t>目的地关税付款状态</t>
   </si>
   <si>
@@ -276,6 +282,9 @@
   </si>
   <si>
     <t>{.freightCurrency}</t>
+  </si>
+  <si>
+    <t>{.billTotalAmount}</t>
   </si>
   <si>
     <t>{.firstMileEstimatedFreightTax}</t>
@@ -1354,7 +1363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BG4"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -1380,40 +1389,40 @@
     <col min="22" max="22" width="11.75" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="10.125" customWidth="1"/>
-    <col min="25" max="25" width="19.25" customWidth="1"/>
-    <col min="26" max="26" width="21.875" customWidth="1"/>
-    <col min="27" max="27" width="20.875" customWidth="1"/>
-    <col min="28" max="28" width="21.125" customWidth="1"/>
-    <col min="30" max="30" width="15.875" customWidth="1"/>
-    <col min="31" max="31" width="17.625" customWidth="1"/>
-    <col min="32" max="32" width="18.75" customWidth="1"/>
-    <col min="33" max="33" width="21" customWidth="1"/>
-    <col min="34" max="34" width="19.375" customWidth="1"/>
-    <col min="35" max="35" width="17.125" customWidth="1"/>
-    <col min="36" max="36" width="19.75" customWidth="1"/>
-    <col min="38" max="38" width="15.75" customWidth="1"/>
-    <col min="39" max="39" width="15.25" customWidth="1"/>
-    <col min="40" max="40" width="18.75" customWidth="1"/>
-    <col min="41" max="41" width="16.625" customWidth="1"/>
-    <col min="42" max="42" width="18.25" customWidth="1"/>
-    <col min="44" max="44" width="14.25" customWidth="1"/>
-    <col min="45" max="45" width="13.625" customWidth="1"/>
-    <col min="46" max="46" width="19" customWidth="1"/>
-    <col min="47" max="47" width="18.75" customWidth="1"/>
-    <col min="48" max="48" width="18.125" customWidth="1"/>
-    <col min="49" max="49" width="15.375" customWidth="1"/>
-    <col min="50" max="50" width="14.625" customWidth="1"/>
-    <col min="51" max="51" width="14.375" customWidth="1"/>
-    <col min="52" max="52" width="16" customWidth="1"/>
-    <col min="53" max="53" width="13.875" customWidth="1"/>
-    <col min="54" max="54" width="14" customWidth="1"/>
-    <col min="55" max="55" width="11.5" customWidth="1"/>
-    <col min="56" max="56" width="15.75" customWidth="1"/>
-    <col min="57" max="57" width="15" customWidth="1"/>
-    <col min="58" max="58" width="14.625" customWidth="1"/>
+    <col min="25" max="26" width="19.25" customWidth="1"/>
+    <col min="27" max="27" width="21.875" customWidth="1"/>
+    <col min="28" max="28" width="20.875" customWidth="1"/>
+    <col min="29" max="29" width="21.125" customWidth="1"/>
+    <col min="31" max="31" width="15.875" customWidth="1"/>
+    <col min="32" max="32" width="17.625" customWidth="1"/>
+    <col min="33" max="33" width="18.75" customWidth="1"/>
+    <col min="34" max="34" width="21" customWidth="1"/>
+    <col min="35" max="35" width="19.375" customWidth="1"/>
+    <col min="36" max="36" width="17.125" customWidth="1"/>
+    <col min="37" max="37" width="19.75" customWidth="1"/>
+    <col min="39" max="39" width="15.75" customWidth="1"/>
+    <col min="40" max="40" width="15.25" customWidth="1"/>
+    <col min="41" max="41" width="18.75" customWidth="1"/>
+    <col min="42" max="42" width="16.625" customWidth="1"/>
+    <col min="43" max="43" width="18.25" customWidth="1"/>
+    <col min="45" max="45" width="14.25" customWidth="1"/>
+    <col min="46" max="46" width="13.625" customWidth="1"/>
+    <col min="47" max="47" width="19" customWidth="1"/>
+    <col min="48" max="48" width="18.75" customWidth="1"/>
+    <col min="49" max="49" width="18.125" customWidth="1"/>
+    <col min="50" max="50" width="15.375" customWidth="1"/>
+    <col min="51" max="51" width="14.625" customWidth="1"/>
+    <col min="52" max="52" width="14.375" customWidth="1"/>
+    <col min="53" max="53" width="16" customWidth="1"/>
+    <col min="54" max="54" width="13.875" customWidth="1"/>
+    <col min="55" max="55" width="14" customWidth="1"/>
+    <col min="56" max="56" width="11.5" customWidth="1"/>
+    <col min="57" max="57" width="15.75" customWidth="1"/>
+    <col min="58" max="58" width="15" customWidth="1"/>
+    <col min="59" max="59" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59">
+    <row r="1" spans="1:60">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1535,247 +1544,253 @@
         <v>39</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:59">
+    <row r="2" spans="1:60">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" spans="43:43">
-      <c r="AQ4" s="2"/>
+    <row r="4" spans="44:44">
+      <c r="AR4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
